--- a/livrables/tbase_par_bande.xlsx
+++ b/livrables/tbase_par_bande.xlsx
@@ -527,22 +527,22 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>99.5</v>
+        <v>109.5</v>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>152.5</v>
+        <v>153.5</v>
       </c>
       <c r="J2" t="n">
-        <v>144.9</v>
+        <v>145.9</v>
       </c>
       <c r="K2" t="n">
-        <v>160.1</v>
+        <v>161.1</v>
       </c>
       <c r="L2" t="n">
         <v>202.5</v>
@@ -569,22 +569,22 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>89.09999999999999</v>
+        <v>103.3</v>
       </c>
       <c r="G3" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
         <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>142.1</v>
+        <v>147.3</v>
       </c>
       <c r="J3" t="n">
-        <v>134.5</v>
+        <v>139.7</v>
       </c>
       <c r="K3" t="n">
-        <v>149.7</v>
+        <v>154.9</v>
       </c>
       <c r="L3" t="n">
         <v>202.5</v>
@@ -611,22 +611,22 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>85.40000000000001</v>
+        <v>102.5</v>
       </c>
       <c r="G4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>138.4</v>
+        <v>146.5</v>
       </c>
       <c r="J4" t="n">
-        <v>130.8</v>
+        <v>138.9</v>
       </c>
       <c r="K4" t="n">
-        <v>146</v>
+        <v>154.1</v>
       </c>
       <c r="L4" t="n">
         <v>202.5</v>
@@ -653,22 +653,22 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>85.09999999999999</v>
+        <v>102.5</v>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>138.1</v>
+        <v>146.5</v>
       </c>
       <c r="J5" t="n">
-        <v>130.5</v>
+        <v>138.9</v>
       </c>
       <c r="K5" t="n">
-        <v>145.7</v>
+        <v>154.1</v>
       </c>
       <c r="L5" t="n">
         <v>202.5</v>
@@ -695,22 +695,22 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>92.90000000000001</v>
+        <v>100.1</v>
       </c>
       <c r="G6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>145.9</v>
+        <v>144.1</v>
       </c>
       <c r="J6" t="n">
-        <v>138.3</v>
+        <v>136.5</v>
       </c>
       <c r="K6" t="n">
-        <v>153.5</v>
+        <v>151.7</v>
       </c>
       <c r="L6" t="n">
         <v>202.5</v>
@@ -737,22 +737,22 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>79.40000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>132.4</v>
+        <v>133.4</v>
       </c>
       <c r="J7" t="n">
-        <v>124.8</v>
+        <v>125.8</v>
       </c>
       <c r="K7" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L7" t="n">
         <v>202.5</v>
@@ -779,22 +779,22 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>71</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>124</v>
+        <v>127.4</v>
       </c>
       <c r="J8" t="n">
-        <v>116.4</v>
+        <v>119.8</v>
       </c>
       <c r="K8" t="n">
-        <v>131.6</v>
+        <v>135</v>
       </c>
       <c r="L8" t="n">
         <v>202.5</v>
@@ -821,22 +821,22 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
         <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="J9" t="n">
-        <v>113.4</v>
+        <v>118.4</v>
       </c>
       <c r="K9" t="n">
-        <v>128.6</v>
+        <v>133.6</v>
       </c>
       <c r="L9" t="n">
         <v>202.5</v>
@@ -863,22 +863,22 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>91.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>144.8</v>
+        <v>142.6</v>
       </c>
       <c r="J10" t="n">
-        <v>137.2</v>
+        <v>135</v>
       </c>
       <c r="K10" t="n">
-        <v>152.4</v>
+        <v>150.2</v>
       </c>
       <c r="L10" t="n">
         <v>202.5</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>75.2</v>
+        <v>84.2</v>
       </c>
       <c r="G11" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
         <v>3</v>
@@ -947,22 +947,22 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>64.90000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="G12" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H12" t="n">
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>117.9</v>
+        <v>120.3</v>
       </c>
       <c r="J12" t="n">
-        <v>110.3</v>
+        <v>112.7</v>
       </c>
       <c r="K12" t="n">
-        <v>125.5</v>
+        <v>127.9</v>
       </c>
       <c r="L12" t="n">
         <v>202.5</v>
@@ -989,22 +989,22 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>59.4</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
         <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>112.4</v>
+        <v>117.4</v>
       </c>
       <c r="J13" t="n">
-        <v>104.8</v>
+        <v>109.8</v>
       </c>
       <c r="K13" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="L13" t="n">
         <v>202.5</v>
@@ -1031,22 +1031,22 @@
         <v>4.5</v>
       </c>
       <c r="F14" t="n">
-        <v>63.6</v>
+        <v>72.2</v>
       </c>
       <c r="G14" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
         <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>106.6</v>
+        <v>106.1</v>
       </c>
       <c r="J14" t="n">
-        <v>101</v>
+        <v>100.5</v>
       </c>
       <c r="K14" t="n">
-        <v>112.2</v>
+        <v>111.7</v>
       </c>
       <c r="L14" t="n">
         <v>122</v>
@@ -1073,22 +1073,22 @@
         <v>4.2</v>
       </c>
       <c r="F15" t="n">
-        <v>55.3</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
         <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>98</v>
+        <v>100.8</v>
       </c>
       <c r="J15" t="n">
-        <v>92.5</v>
+        <v>95.2</v>
       </c>
       <c r="K15" t="n">
-        <v>103.5</v>
+        <v>106.3</v>
       </c>
       <c r="L15" t="n">
         <v>122</v>
@@ -1115,22 +1115,22 @@
         <v>3.9</v>
       </c>
       <c r="F16" t="n">
-        <v>50.2</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
         <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>92.59999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>87.09999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>98.09999999999999</v>
+        <v>104.1</v>
       </c>
       <c r="L16" t="n">
         <v>122</v>
@@ -1157,22 +1157,22 @@
         <v>3.8</v>
       </c>
       <c r="F17" t="n">
-        <v>48.2</v>
+        <v>64.7</v>
       </c>
       <c r="G17" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
         <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>90.5</v>
+        <v>98</v>
       </c>
       <c r="J17" t="n">
-        <v>85.09999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="K17" t="n">
-        <v>96</v>
+        <v>103.4</v>
       </c>
       <c r="L17" t="n">
         <v>122</v>
@@ -1199,22 +1199,22 @@
         <v>4.5</v>
       </c>
       <c r="F18" t="n">
-        <v>59.6</v>
+        <v>66.3</v>
       </c>
       <c r="G18" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H18" t="n">
         <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>102.5</v>
+        <v>100.3</v>
       </c>
       <c r="J18" t="n">
-        <v>96.90000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="K18" t="n">
-        <v>108.1</v>
+        <v>105.8</v>
       </c>
       <c r="L18" t="n">
         <v>122</v>
@@ -1241,22 +1241,22 @@
         <v>4.2</v>
       </c>
       <c r="F19" t="n">
-        <v>50.8</v>
+        <v>59.5</v>
       </c>
       <c r="G19" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H19" t="n">
         <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>93.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>87.90000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>99</v>
+        <v>98.7</v>
       </c>
       <c r="L19" t="n">
         <v>122</v>
@@ -1283,22 +1283,22 @@
         <v>3.9</v>
       </c>
       <c r="F20" t="n">
-        <v>44.1</v>
+        <v>54.7</v>
       </c>
       <c r="G20" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H20" t="n">
         <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>86.59999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>81.09999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>92.09999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="L20" t="n">
         <v>122</v>
@@ -1325,22 +1325,22 @@
         <v>3.8</v>
       </c>
       <c r="F21" t="n">
-        <v>40.6</v>
+        <v>52.7</v>
       </c>
       <c r="G21" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H21" t="n">
         <v>3</v>
       </c>
       <c r="I21" t="n">
-        <v>82.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="J21" t="n">
-        <v>77.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="K21" t="n">
-        <v>88.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L21" t="n">
         <v>122</v>
@@ -1367,22 +1367,22 @@
         <v>4.5</v>
       </c>
       <c r="F22" t="n">
-        <v>59</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H22" t="n">
         <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>102</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>96.40000000000001</v>
+        <v>94</v>
       </c>
       <c r="K22" t="n">
-        <v>107.6</v>
+        <v>105.2</v>
       </c>
       <c r="L22" t="n">
         <v>122</v>
@@ -1409,22 +1409,22 @@
         <v>4.2</v>
       </c>
       <c r="F23" t="n">
-        <v>48.2</v>
+        <v>56.7</v>
       </c>
       <c r="G23" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H23" t="n">
         <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>90.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>85.3</v>
+        <v>84.8</v>
       </c>
       <c r="K23" t="n">
-        <v>96.40000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="L23" t="n">
         <v>122</v>
@@ -1451,22 +1451,22 @@
         <v>3.9</v>
       </c>
       <c r="F24" t="n">
-        <v>41.3</v>
+        <v>51.3</v>
       </c>
       <c r="G24" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H24" t="n">
         <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>83.7</v>
+        <v>84.8</v>
       </c>
       <c r="J24" t="n">
-        <v>78.2</v>
+        <v>79.3</v>
       </c>
       <c r="K24" t="n">
-        <v>89.2</v>
+        <v>90.3</v>
       </c>
       <c r="L24" t="n">
         <v>122</v>
@@ -1493,22 +1493,22 @@
         <v>3.8</v>
       </c>
       <c r="F25" t="n">
-        <v>36.9</v>
+        <v>49</v>
       </c>
       <c r="G25" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>79.2</v>
+        <v>82.3</v>
       </c>
       <c r="J25" t="n">
-        <v>73.7</v>
+        <v>76.8</v>
       </c>
       <c r="K25" t="n">
-        <v>84.59999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="L25" t="n">
         <v>122</v>
@@ -1535,22 +1535,22 @@
         <v>4.6</v>
       </c>
       <c r="F26" t="n">
-        <v>160.7</v>
+        <v>182.4</v>
       </c>
       <c r="G26" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H26" t="n">
         <v>10</v>
       </c>
       <c r="I26" t="n">
-        <v>233.2</v>
+        <v>224.9</v>
       </c>
       <c r="J26" t="n">
-        <v>228.7</v>
+        <v>220.4</v>
       </c>
       <c r="K26" t="n">
-        <v>237.7</v>
+        <v>229.4</v>
       </c>
       <c r="L26" t="n">
         <v>275</v>
@@ -1577,22 +1577,22 @@
         <v>4.4</v>
       </c>
       <c r="F27" t="n">
-        <v>138.5</v>
+        <v>167.8</v>
       </c>
       <c r="G27" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H27" t="n">
         <v>10</v>
       </c>
       <c r="I27" t="n">
-        <v>211</v>
+        <v>210.3</v>
       </c>
       <c r="J27" t="n">
-        <v>206.5</v>
+        <v>205.8</v>
       </c>
       <c r="K27" t="n">
-        <v>215.4</v>
+        <v>214.8</v>
       </c>
       <c r="L27" t="n">
         <v>275</v>
@@ -1619,22 +1619,22 @@
         <v>4.4</v>
       </c>
       <c r="F28" t="n">
-        <v>128.3</v>
+        <v>164.7</v>
       </c>
       <c r="G28" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H28" t="n">
         <v>10</v>
       </c>
       <c r="I28" t="n">
-        <v>200.7</v>
+        <v>207.1</v>
       </c>
       <c r="J28" t="n">
-        <v>196.2</v>
+        <v>202.6</v>
       </c>
       <c r="K28" t="n">
-        <v>205.2</v>
+        <v>211.5</v>
       </c>
       <c r="L28" t="n">
         <v>275</v>
@@ -1661,22 +1661,22 @@
         <v>4.4</v>
       </c>
       <c r="F29" t="n">
-        <v>125.8</v>
+        <v>164.5</v>
       </c>
       <c r="G29" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H29" t="n">
         <v>10</v>
       </c>
       <c r="I29" t="n">
-        <v>198.2</v>
+        <v>206.9</v>
       </c>
       <c r="J29" t="n">
-        <v>193.7</v>
+        <v>202.4</v>
       </c>
       <c r="K29" t="n">
-        <v>202.6</v>
+        <v>211.4</v>
       </c>
       <c r="L29" t="n">
         <v>275</v>
@@ -1703,22 +1703,22 @@
         <v>4.6</v>
       </c>
       <c r="F30" t="n">
-        <v>157</v>
+        <v>173.7</v>
       </c>
       <c r="G30" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H30" t="n">
         <v>10</v>
       </c>
       <c r="I30" t="n">
-        <v>229.6</v>
+        <v>216.3</v>
       </c>
       <c r="J30" t="n">
-        <v>225.1</v>
+        <v>211.8</v>
       </c>
       <c r="K30" t="n">
-        <v>234.1</v>
+        <v>220.8</v>
       </c>
       <c r="L30" t="n">
         <v>275</v>
@@ -1745,22 +1745,22 @@
         <v>4.4</v>
       </c>
       <c r="F31" t="n">
-        <v>128.3</v>
+        <v>150.4</v>
       </c>
       <c r="G31" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H31" t="n">
         <v>10</v>
       </c>
       <c r="I31" t="n">
-        <v>200.8</v>
+        <v>192.8</v>
       </c>
       <c r="J31" t="n">
-        <v>196.3</v>
+        <v>188.3</v>
       </c>
       <c r="K31" t="n">
-        <v>205.3</v>
+        <v>197.3</v>
       </c>
       <c r="L31" t="n">
         <v>275</v>
@@ -1787,22 +1787,22 @@
         <v>4.4</v>
       </c>
       <c r="F32" t="n">
-        <v>110.5</v>
+        <v>136.7</v>
       </c>
       <c r="G32" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H32" t="n">
         <v>10</v>
       </c>
       <c r="I32" t="n">
-        <v>182.9</v>
+        <v>179.1</v>
       </c>
       <c r="J32" t="n">
-        <v>178.4</v>
+        <v>174.6</v>
       </c>
       <c r="K32" t="n">
-        <v>187.3</v>
+        <v>183.5</v>
       </c>
       <c r="L32" t="n">
         <v>275</v>
@@ -1829,22 +1829,22 @@
         <v>4.4</v>
       </c>
       <c r="F33" t="n">
-        <v>103</v>
+        <v>132.8</v>
       </c>
       <c r="G33" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H33" t="n">
         <v>10</v>
       </c>
       <c r="I33" t="n">
-        <v>175.3</v>
+        <v>175.1</v>
       </c>
       <c r="J33" t="n">
-        <v>170.9</v>
+        <v>170.7</v>
       </c>
       <c r="K33" t="n">
-        <v>179.8</v>
+        <v>179.6</v>
       </c>
       <c r="L33" t="n">
         <v>275</v>
@@ -1871,22 +1871,22 @@
         <v>4.6</v>
       </c>
       <c r="F34" t="n">
-        <v>155.7</v>
+        <v>172.2</v>
       </c>
       <c r="G34" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H34" t="n">
         <v>10</v>
       </c>
       <c r="I34" t="n">
-        <v>228.2</v>
+        <v>214.7</v>
       </c>
       <c r="J34" t="n">
-        <v>223.7</v>
+        <v>210.2</v>
       </c>
       <c r="K34" t="n">
-        <v>232.8</v>
+        <v>219.2</v>
       </c>
       <c r="L34" t="n">
         <v>275</v>
@@ -1913,22 +1913,22 @@
         <v>4.4</v>
       </c>
       <c r="F35" t="n">
-        <v>126</v>
+        <v>147.2</v>
       </c>
       <c r="G35" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H35" t="n">
         <v>10</v>
       </c>
       <c r="I35" t="n">
-        <v>198.5</v>
+        <v>189.7</v>
       </c>
       <c r="J35" t="n">
-        <v>194</v>
+        <v>185.2</v>
       </c>
       <c r="K35" t="n">
-        <v>202.9</v>
+        <v>194.2</v>
       </c>
       <c r="L35" t="n">
         <v>275</v>
@@ -1955,22 +1955,22 @@
         <v>4.4</v>
       </c>
       <c r="F36" t="n">
-        <v>103.9</v>
+        <v>129.4</v>
       </c>
       <c r="G36" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H36" t="n">
         <v>10</v>
       </c>
       <c r="I36" t="n">
-        <v>176.3</v>
+        <v>171.7</v>
       </c>
       <c r="J36" t="n">
-        <v>171.8</v>
+        <v>167.3</v>
       </c>
       <c r="K36" t="n">
-        <v>180.8</v>
+        <v>176.2</v>
       </c>
       <c r="L36" t="n">
         <v>275</v>
@@ -1997,22 +1997,22 @@
         <v>4.4</v>
       </c>
       <c r="F37" t="n">
-        <v>92.3</v>
+        <v>122.4</v>
       </c>
       <c r="G37" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H37" t="n">
         <v>10</v>
       </c>
       <c r="I37" t="n">
-        <v>164.7</v>
+        <v>164.8</v>
       </c>
       <c r="J37" t="n">
-        <v>160.2</v>
+        <v>160.3</v>
       </c>
       <c r="K37" t="n">
-        <v>169.1</v>
+        <v>169.3</v>
       </c>
       <c r="L37" t="n">
         <v>275</v>
@@ -2039,22 +2039,22 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>191.4</v>
+        <v>212.9</v>
       </c>
       <c r="G38" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="H38" t="n">
         <v>9</v>
       </c>
       <c r="I38" t="n">
-        <v>277.9</v>
+        <v>272.4</v>
       </c>
       <c r="J38" t="n">
-        <v>269.6</v>
+        <v>264.1</v>
       </c>
       <c r="K38" t="n">
-        <v>286.2</v>
+        <v>280.7</v>
       </c>
       <c r="L38" t="n">
         <v>318</v>
@@ -2081,22 +2081,22 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>162</v>
+        <v>191.8</v>
       </c>
       <c r="G39" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="H39" t="n">
         <v>9</v>
       </c>
       <c r="I39" t="n">
-        <v>248.5</v>
+        <v>251.3</v>
       </c>
       <c r="J39" t="n">
-        <v>240.2</v>
+        <v>243</v>
       </c>
       <c r="K39" t="n">
-        <v>256.8</v>
+        <v>259.6</v>
       </c>
       <c r="L39" t="n">
         <v>318</v>
@@ -2123,22 +2123,22 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>146.6</v>
+        <v>184.7</v>
       </c>
       <c r="G40" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="H40" t="n">
         <v>9</v>
       </c>
       <c r="I40" t="n">
-        <v>233.1</v>
+        <v>244.2</v>
       </c>
       <c r="J40" t="n">
-        <v>224.8</v>
+        <v>235.9</v>
       </c>
       <c r="K40" t="n">
-        <v>241.4</v>
+        <v>252.5</v>
       </c>
       <c r="L40" t="n">
         <v>318</v>
@@ -2165,22 +2165,22 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>143.1</v>
+        <v>183.9</v>
       </c>
       <c r="G41" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="H41" t="n">
         <v>9</v>
       </c>
       <c r="I41" t="n">
-        <v>229.6</v>
+        <v>243.4</v>
       </c>
       <c r="J41" t="n">
-        <v>221.3</v>
+        <v>235.1</v>
       </c>
       <c r="K41" t="n">
-        <v>237.9</v>
+        <v>251.7</v>
       </c>
       <c r="L41" t="n">
         <v>318</v>
@@ -2207,22 +2207,22 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>188.3</v>
+        <v>204.8</v>
       </c>
       <c r="G42" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="H42" t="n">
         <v>9</v>
       </c>
       <c r="I42" t="n">
-        <v>274.8</v>
+        <v>264.3</v>
       </c>
       <c r="J42" t="n">
-        <v>266.5</v>
+        <v>256</v>
       </c>
       <c r="K42" t="n">
-        <v>283.1</v>
+        <v>272.6</v>
       </c>
       <c r="L42" t="n">
         <v>318</v>
@@ -2249,22 +2249,22 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>153</v>
+        <v>174.6</v>
       </c>
       <c r="G43" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="H43" t="n">
         <v>9</v>
       </c>
       <c r="I43" t="n">
-        <v>239.5</v>
+        <v>234.1</v>
       </c>
       <c r="J43" t="n">
-        <v>231.2</v>
+        <v>225.8</v>
       </c>
       <c r="K43" t="n">
-        <v>247.8</v>
+        <v>242.4</v>
       </c>
       <c r="L43" t="n">
         <v>318</v>
@@ -2291,22 +2291,22 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>129.3</v>
+        <v>155.6</v>
       </c>
       <c r="G44" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="H44" t="n">
         <v>9</v>
       </c>
       <c r="I44" t="n">
-        <v>215.8</v>
+        <v>215.1</v>
       </c>
       <c r="J44" t="n">
-        <v>207.5</v>
+        <v>206.8</v>
       </c>
       <c r="K44" t="n">
-        <v>224.1</v>
+        <v>223.4</v>
       </c>
       <c r="L44" t="n">
         <v>318</v>
@@ -2333,22 +2333,22 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>117.8</v>
+        <v>148.5</v>
       </c>
       <c r="G45" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="H45" t="n">
         <v>9</v>
       </c>
       <c r="I45" t="n">
-        <v>204.3</v>
+        <v>208</v>
       </c>
       <c r="J45" t="n">
-        <v>196</v>
+        <v>199.7</v>
       </c>
       <c r="K45" t="n">
-        <v>212.6</v>
+        <v>216.3</v>
       </c>
       <c r="L45" t="n">
         <v>318</v>
@@ -2375,22 +2375,22 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>187.4</v>
+        <v>203.4</v>
       </c>
       <c r="G46" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="H46" t="n">
         <v>9</v>
       </c>
       <c r="I46" t="n">
-        <v>273.9</v>
+        <v>262.9</v>
       </c>
       <c r="J46" t="n">
-        <v>265.6</v>
+        <v>254.6</v>
       </c>
       <c r="K46" t="n">
-        <v>282.2</v>
+        <v>271.2</v>
       </c>
       <c r="L46" t="n">
         <v>318</v>
@@ -2417,22 +2417,22 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>151</v>
+        <v>171.7</v>
       </c>
       <c r="G47" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="H47" t="n">
         <v>9</v>
       </c>
       <c r="I47" t="n">
-        <v>237.5</v>
+        <v>231.2</v>
       </c>
       <c r="J47" t="n">
-        <v>229.2</v>
+        <v>222.9</v>
       </c>
       <c r="K47" t="n">
-        <v>245.8</v>
+        <v>239.5</v>
       </c>
       <c r="L47" t="n">
         <v>318</v>
@@ -2459,22 +2459,22 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>123.4</v>
+        <v>148.2</v>
       </c>
       <c r="G48" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="H48" t="n">
         <v>9</v>
       </c>
       <c r="I48" t="n">
-        <v>209.9</v>
+        <v>207.7</v>
       </c>
       <c r="J48" t="n">
-        <v>201.6</v>
+        <v>199.4</v>
       </c>
       <c r="K48" t="n">
-        <v>218.2</v>
+        <v>216</v>
       </c>
       <c r="L48" t="n">
         <v>318</v>
@@ -2501,22 +2501,22 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="G49" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="H49" t="n">
         <v>9</v>
       </c>
       <c r="I49" t="n">
-        <v>194.5</v>
+        <v>197.5</v>
       </c>
       <c r="J49" t="n">
-        <v>186.2</v>
+        <v>189.2</v>
       </c>
       <c r="K49" t="n">
-        <v>202.8</v>
+        <v>205.8</v>
       </c>
       <c r="L49" t="n">
         <v>318</v>

--- a/livrables/tbase_par_bande.xlsx
+++ b/livrables/tbase_par_bande.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tbase_par_bande" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'tbase_par_bande'!$A$1:$L$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'tbase_par_bande'!$A$1:$L$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>109.5</v>
+        <v>109.2</v>
       </c>
       <c r="G2" t="n">
         <v>6</v>
@@ -536,13 +536,13 @@
         <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>153.5</v>
+        <v>153.2</v>
       </c>
       <c r="J2" t="n">
-        <v>145.9</v>
+        <v>145.6</v>
       </c>
       <c r="K2" t="n">
-        <v>161.1</v>
+        <v>160.8</v>
       </c>
       <c r="L2" t="n">
         <v>202.5</v>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D3" t="n">
         <v>38</v>
@@ -569,7 +569,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>103.3</v>
+        <v>105.5</v>
       </c>
       <c r="G3" t="n">
         <v>6</v>
@@ -578,13 +578,13 @@
         <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>147.3</v>
+        <v>149.5</v>
       </c>
       <c r="J3" t="n">
-        <v>139.7</v>
+        <v>141.9</v>
       </c>
       <c r="K3" t="n">
-        <v>154.9</v>
+        <v>157.1</v>
       </c>
       <c r="L3" t="n">
         <v>202.5</v>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="D4" t="n">
         <v>38</v>
@@ -611,7 +611,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>102.5</v>
+        <v>102.6</v>
       </c>
       <c r="G4" t="n">
         <v>6</v>
@@ -620,13 +620,13 @@
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>146.5</v>
+        <v>146.6</v>
       </c>
       <c r="J4" t="n">
-        <v>138.9</v>
+        <v>139</v>
       </c>
       <c r="K4" t="n">
-        <v>154.1</v>
+        <v>154.2</v>
       </c>
       <c r="L4" t="n">
         <v>202.5</v>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="D5" t="n">
         <v>38</v>
@@ -653,7 +653,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>102.5</v>
+        <v>101.4</v>
       </c>
       <c r="G5" t="n">
         <v>6</v>
@@ -662,13 +662,13 @@
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>146.5</v>
+        <v>145.4</v>
       </c>
       <c r="J5" t="n">
-        <v>138.9</v>
+        <v>137.8</v>
       </c>
       <c r="K5" t="n">
-        <v>154.1</v>
+        <v>153</v>
       </c>
       <c r="L5" t="n">
         <v>202.5</v>
@@ -682,11 +682,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>160</v>
+        <v>300</v>
       </c>
       <c r="D6" t="n">
         <v>38</v>
@@ -695,7 +695,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>100.1</v>
+        <v>101.4</v>
       </c>
       <c r="G6" t="n">
         <v>6</v>
@@ -704,13 +704,13 @@
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>144.1</v>
+        <v>145.4</v>
       </c>
       <c r="J6" t="n">
-        <v>136.5</v>
+        <v>137.8</v>
       </c>
       <c r="K6" t="n">
-        <v>151.7</v>
+        <v>153</v>
       </c>
       <c r="L6" t="n">
         <v>202.5</v>
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="D7" t="n">
         <v>38</v>
@@ -737,7 +737,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>89.40000000000001</v>
+        <v>100.3</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
@@ -746,13 +746,13 @@
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>133.4</v>
+        <v>144.3</v>
       </c>
       <c r="J7" t="n">
-        <v>125.8</v>
+        <v>136.7</v>
       </c>
       <c r="K7" t="n">
-        <v>141</v>
+        <v>151.9</v>
       </c>
       <c r="L7" t="n">
         <v>202.5</v>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>250</v>
+        <v>177</v>
       </c>
       <c r="D8" t="n">
         <v>38</v>
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>83.40000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="G8" t="n">
         <v>6</v>
@@ -788,13 +788,13 @@
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>127.4</v>
+        <v>138.5</v>
       </c>
       <c r="J8" t="n">
-        <v>119.8</v>
+        <v>130.9</v>
       </c>
       <c r="K8" t="n">
-        <v>135</v>
+        <v>146.1</v>
       </c>
       <c r="L8" t="n">
         <v>202.5</v>
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D9" t="n">
         <v>38</v>
@@ -821,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>82</v>
+        <v>89.2</v>
       </c>
       <c r="G9" t="n">
         <v>6</v>
@@ -830,13 +830,13 @@
         <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>126</v>
+        <v>133.2</v>
       </c>
       <c r="J9" t="n">
-        <v>118.4</v>
+        <v>125.6</v>
       </c>
       <c r="K9" t="n">
-        <v>133.6</v>
+        <v>140.8</v>
       </c>
       <c r="L9" t="n">
         <v>202.5</v>
@@ -850,11 +850,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="D10" t="n">
         <v>38</v>
@@ -863,7 +863,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>98.59999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>6</v>
@@ -872,13 +872,13 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>142.6</v>
+        <v>126.9</v>
       </c>
       <c r="J10" t="n">
-        <v>135</v>
+        <v>119.3</v>
       </c>
       <c r="K10" t="n">
-        <v>150.2</v>
+        <v>134.5</v>
       </c>
       <c r="L10" t="n">
         <v>202.5</v>
@@ -892,11 +892,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D11" t="n">
         <v>38</v>
@@ -905,7 +905,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>84.2</v>
+        <v>81.2</v>
       </c>
       <c r="G11" t="n">
         <v>6</v>
@@ -914,13 +914,13 @@
         <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>128.2</v>
+        <v>125.2</v>
       </c>
       <c r="J11" t="n">
-        <v>120.6</v>
+        <v>117.6</v>
       </c>
       <c r="K11" t="n">
-        <v>135.8</v>
+        <v>132.8</v>
       </c>
       <c r="L11" t="n">
         <v>202.5</v>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
         <v>38</v>
@@ -947,7 +947,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>76.3</v>
+        <v>98.8</v>
       </c>
       <c r="G12" t="n">
         <v>6</v>
@@ -956,13 +956,13 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>120.3</v>
+        <v>142.8</v>
       </c>
       <c r="J12" t="n">
-        <v>112.7</v>
+        <v>135.2</v>
       </c>
       <c r="K12" t="n">
-        <v>127.9</v>
+        <v>150.4</v>
       </c>
       <c r="L12" t="n">
         <v>202.5</v>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>300</v>
+        <v>177</v>
       </c>
       <c r="D13" t="n">
         <v>38</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>73.40000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>6</v>
@@ -998,13 +998,13 @@
         <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>117.4</v>
+        <v>135.1</v>
       </c>
       <c r="J13" t="n">
-        <v>109.8</v>
+        <v>127.5</v>
       </c>
       <c r="K13" t="n">
-        <v>125</v>
+        <v>142.7</v>
       </c>
       <c r="L13" t="n">
         <v>202.5</v>
@@ -1013,25 +1013,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MTL-Ott</t>
+          <t>MTL-QC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="D14" t="n">
-        <v>23.5</v>
+        <v>38</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>72.2</v>
+        <v>84.3</v>
       </c>
       <c r="G14" t="n">
         <v>6</v>
@@ -1040,40 +1040,40 @@
         <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>106.1</v>
+        <v>128.3</v>
       </c>
       <c r="J14" t="n">
-        <v>100.5</v>
+        <v>120.7</v>
       </c>
       <c r="K14" t="n">
-        <v>111.7</v>
+        <v>135.9</v>
       </c>
       <c r="L14" t="n">
-        <v>122</v>
+        <v>202.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MTL-Ott</t>
+          <t>MTL-QC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="D15" t="n">
-        <v>23.5</v>
+        <v>38</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>67.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="G15" t="n">
         <v>6</v>
@@ -1082,40 +1082,40 @@
         <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>100.8</v>
+        <v>120.2</v>
       </c>
       <c r="J15" t="n">
-        <v>95.2</v>
+        <v>112.6</v>
       </c>
       <c r="K15" t="n">
-        <v>106.3</v>
+        <v>127.8</v>
       </c>
       <c r="L15" t="n">
-        <v>122</v>
+        <v>202.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MTL-Ott</t>
+          <t>MTL-QC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="D16" t="n">
-        <v>23.5</v>
+        <v>38</v>
       </c>
       <c r="E16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>65.09999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>6</v>
@@ -1124,16 +1124,16 @@
         <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>98.59999999999999</v>
+        <v>117.1</v>
       </c>
       <c r="J16" t="n">
-        <v>93.09999999999999</v>
+        <v>109.5</v>
       </c>
       <c r="K16" t="n">
-        <v>104.1</v>
+        <v>124.7</v>
       </c>
       <c r="L16" t="n">
-        <v>122</v>
+        <v>202.5</v>
       </c>
     </row>
     <row r="17">
@@ -1148,16 +1148,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="D17" t="n">
         <v>23.5</v>
       </c>
       <c r="E17" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="F17" t="n">
-        <v>64.7</v>
+        <v>75.8</v>
       </c>
       <c r="G17" t="n">
         <v>6</v>
@@ -1166,13 +1166,13 @@
         <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>98</v>
+        <v>109.9</v>
       </c>
       <c r="J17" t="n">
-        <v>92.5</v>
+        <v>104.3</v>
       </c>
       <c r="K17" t="n">
-        <v>103.4</v>
+        <v>115.5</v>
       </c>
       <c r="L17" t="n">
         <v>122</v>
@@ -1186,11 +1186,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="D18" t="n">
         <v>23.5</v>
@@ -1199,7 +1199,7 @@
         <v>4.5</v>
       </c>
       <c r="F18" t="n">
-        <v>66.3</v>
+        <v>74.3</v>
       </c>
       <c r="G18" t="n">
         <v>6</v>
@@ -1208,13 +1208,13 @@
         <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>100.3</v>
+        <v>108.4</v>
       </c>
       <c r="J18" t="n">
-        <v>94.7</v>
+        <v>102.7</v>
       </c>
       <c r="K18" t="n">
-        <v>105.8</v>
+        <v>114</v>
       </c>
       <c r="L18" t="n">
         <v>122</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1238,10 +1238,10 @@
         <v>23.5</v>
       </c>
       <c r="E19" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="F19" t="n">
-        <v>59.5</v>
+        <v>73.2</v>
       </c>
       <c r="G19" t="n">
         <v>6</v>
@@ -1250,13 +1250,13 @@
         <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>93.09999999999999</v>
+        <v>107.1</v>
       </c>
       <c r="J19" t="n">
-        <v>87.59999999999999</v>
+        <v>101.5</v>
       </c>
       <c r="K19" t="n">
-        <v>98.7</v>
+        <v>112.7</v>
       </c>
       <c r="L19" t="n">
         <v>122</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1280,10 +1280,10 @@
         <v>23.5</v>
       </c>
       <c r="E20" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="F20" t="n">
-        <v>54.7</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G20" t="n">
         <v>6</v>
@@ -1292,13 +1292,13 @@
         <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>88.09999999999999</v>
+        <v>106.3</v>
       </c>
       <c r="J20" t="n">
-        <v>82.59999999999999</v>
+        <v>100.7</v>
       </c>
       <c r="K20" t="n">
-        <v>93.59999999999999</v>
+        <v>111.8</v>
       </c>
       <c r="L20" t="n">
         <v>122</v>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1322,10 +1322,10 @@
         <v>23.5</v>
       </c>
       <c r="E21" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="F21" t="n">
-        <v>52.7</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>6</v>
@@ -1334,13 +1334,13 @@
         <v>3</v>
       </c>
       <c r="I21" t="n">
-        <v>86</v>
+        <v>106.2</v>
       </c>
       <c r="J21" t="n">
-        <v>80.5</v>
+        <v>100.7</v>
       </c>
       <c r="K21" t="n">
-        <v>91.40000000000001</v>
+        <v>111.8</v>
       </c>
       <c r="L21" t="n">
         <v>122</v>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1364,10 +1364,10 @@
         <v>23.5</v>
       </c>
       <c r="E22" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="F22" t="n">
-        <v>65.59999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>6</v>
@@ -1376,13 +1376,13 @@
         <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>99.59999999999999</v>
+        <v>100.2</v>
       </c>
       <c r="J22" t="n">
-        <v>94</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>105.2</v>
+        <v>105.9</v>
       </c>
       <c r="L22" t="n">
         <v>122</v>
@@ -1396,20 +1396,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D23" t="n">
         <v>23.5</v>
       </c>
       <c r="E23" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="F23" t="n">
-        <v>56.7</v>
+        <v>63.9</v>
       </c>
       <c r="G23" t="n">
         <v>6</v>
@@ -1418,13 +1418,13 @@
         <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>90.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="J23" t="n">
-        <v>84.8</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>95.90000000000001</v>
+        <v>103.6</v>
       </c>
       <c r="L23" t="n">
         <v>122</v>
@@ -1438,20 +1438,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="D24" t="n">
         <v>23.5</v>
       </c>
       <c r="E24" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="F24" t="n">
-        <v>51.3</v>
+        <v>62.1</v>
       </c>
       <c r="G24" t="n">
         <v>6</v>
@@ -1460,13 +1460,13 @@
         <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>84.8</v>
+        <v>96</v>
       </c>
       <c r="J24" t="n">
-        <v>79.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>90.3</v>
+        <v>101.6</v>
       </c>
       <c r="L24" t="n">
         <v>122</v>
@@ -1480,20 +1480,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="D25" t="n">
         <v>23.5</v>
       </c>
       <c r="E25" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="F25" t="n">
-        <v>49</v>
+        <v>59.3</v>
       </c>
       <c r="G25" t="n">
         <v>6</v>
@@ -1502,13 +1502,13 @@
         <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>82.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>76.8</v>
+        <v>87.5</v>
       </c>
       <c r="K25" t="n">
-        <v>87.7</v>
+        <v>98.7</v>
       </c>
       <c r="L25" t="n">
         <v>122</v>
@@ -1517,253 +1517,253 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>160</v>
+        <v>300</v>
       </c>
       <c r="D26" t="n">
-        <v>18</v>
+        <v>23.5</v>
       </c>
       <c r="E26" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="F26" t="n">
-        <v>182.4</v>
+        <v>58.3</v>
       </c>
       <c r="G26" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H26" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>224.9</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>220.4</v>
+        <v>86.5</v>
       </c>
       <c r="K26" t="n">
-        <v>229.4</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="D27" t="n">
-        <v>18</v>
+        <v>23.5</v>
       </c>
       <c r="E27" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="F27" t="n">
-        <v>167.8</v>
+        <v>65.5</v>
       </c>
       <c r="G27" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H27" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>210.3</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>205.8</v>
+        <v>94</v>
       </c>
       <c r="K27" t="n">
-        <v>214.8</v>
+        <v>105.2</v>
       </c>
       <c r="L27" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>250</v>
+        <v>177</v>
       </c>
       <c r="D28" t="n">
-        <v>18</v>
+        <v>23.5</v>
       </c>
       <c r="E28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="F28" t="n">
-        <v>164.7</v>
+        <v>60.7</v>
       </c>
       <c r="G28" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H28" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I28" t="n">
-        <v>207.1</v>
+        <v>94.7</v>
       </c>
       <c r="J28" t="n">
-        <v>202.6</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>211.5</v>
+        <v>100.3</v>
       </c>
       <c r="L28" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D29" t="n">
-        <v>18</v>
+        <v>23.5</v>
       </c>
       <c r="E29" t="n">
         <v>4.4</v>
       </c>
       <c r="F29" t="n">
-        <v>164.5</v>
+        <v>56.9</v>
       </c>
       <c r="G29" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
-        <v>206.9</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>202.4</v>
+        <v>85.3</v>
       </c>
       <c r="K29" t="n">
-        <v>211.4</v>
+        <v>96.5</v>
       </c>
       <c r="L29" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="D30" t="n">
-        <v>18</v>
+        <v>23.5</v>
       </c>
       <c r="E30" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="F30" t="n">
-        <v>173.7</v>
+        <v>53.7</v>
       </c>
       <c r="G30" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H30" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
-        <v>216.3</v>
+        <v>87.5</v>
       </c>
       <c r="J30" t="n">
-        <v>211.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>220.8</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D31" t="n">
-        <v>18</v>
+        <v>23.5</v>
       </c>
       <c r="E31" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="F31" t="n">
-        <v>150.4</v>
+        <v>52.3</v>
       </c>
       <c r="G31" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H31" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I31" t="n">
-        <v>192.8</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>188.3</v>
+        <v>80.5</v>
       </c>
       <c r="K31" t="n">
-        <v>197.3</v>
+        <v>91.7</v>
       </c>
       <c r="L31" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32">
@@ -1774,20 +1774,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="D32" t="n">
         <v>18</v>
       </c>
       <c r="E32" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="F32" t="n">
-        <v>136.7</v>
+        <v>179.6</v>
       </c>
       <c r="G32" t="n">
         <v>20</v>
@@ -1796,13 +1796,13 @@
         <v>10</v>
       </c>
       <c r="I32" t="n">
-        <v>179.1</v>
+        <v>222.1</v>
       </c>
       <c r="J32" t="n">
-        <v>174.6</v>
+        <v>217.6</v>
       </c>
       <c r="K32" t="n">
-        <v>183.5</v>
+        <v>226.6</v>
       </c>
       <c r="L32" t="n">
         <v>275</v>
@@ -1816,20 +1816,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>300</v>
+        <v>177</v>
       </c>
       <c r="D33" t="n">
         <v>18</v>
       </c>
       <c r="E33" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="F33" t="n">
-        <v>132.8</v>
+        <v>171.1</v>
       </c>
       <c r="G33" t="n">
         <v>20</v>
@@ -1838,13 +1838,13 @@
         <v>10</v>
       </c>
       <c r="I33" t="n">
-        <v>175.1</v>
+        <v>213.6</v>
       </c>
       <c r="J33" t="n">
-        <v>170.7</v>
+        <v>209.1</v>
       </c>
       <c r="K33" t="n">
-        <v>179.6</v>
+        <v>218.1</v>
       </c>
       <c r="L33" t="n">
         <v>275</v>
@@ -1858,20 +1858,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="D34" t="n">
         <v>18</v>
       </c>
       <c r="E34" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="F34" t="n">
-        <v>172.2</v>
+        <v>164.4</v>
       </c>
       <c r="G34" t="n">
         <v>20</v>
@@ -1880,13 +1880,13 @@
         <v>10</v>
       </c>
       <c r="I34" t="n">
-        <v>214.7</v>
+        <v>206.8</v>
       </c>
       <c r="J34" t="n">
-        <v>210.2</v>
+        <v>202.3</v>
       </c>
       <c r="K34" t="n">
-        <v>219.2</v>
+        <v>211.3</v>
       </c>
       <c r="L34" t="n">
         <v>275</v>
@@ -1900,11 +1900,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="D35" t="n">
         <v>18</v>
@@ -1913,7 +1913,7 @@
         <v>4.4</v>
       </c>
       <c r="F35" t="n">
-        <v>147.2</v>
+        <v>160.3</v>
       </c>
       <c r="G35" t="n">
         <v>20</v>
@@ -1922,13 +1922,13 @@
         <v>10</v>
       </c>
       <c r="I35" t="n">
-        <v>189.7</v>
+        <v>202.7</v>
       </c>
       <c r="J35" t="n">
-        <v>185.2</v>
+        <v>198.2</v>
       </c>
       <c r="K35" t="n">
-        <v>194.2</v>
+        <v>207.2</v>
       </c>
       <c r="L35" t="n">
         <v>275</v>
@@ -1942,11 +1942,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="D36" t="n">
         <v>18</v>
@@ -1955,7 +1955,7 @@
         <v>4.4</v>
       </c>
       <c r="F36" t="n">
-        <v>129.4</v>
+        <v>160.2</v>
       </c>
       <c r="G36" t="n">
         <v>20</v>
@@ -1964,13 +1964,13 @@
         <v>10</v>
       </c>
       <c r="I36" t="n">
-        <v>171.7</v>
+        <v>202.5</v>
       </c>
       <c r="J36" t="n">
-        <v>167.3</v>
+        <v>198.1</v>
       </c>
       <c r="K36" t="n">
-        <v>176.2</v>
+        <v>207</v>
       </c>
       <c r="L36" t="n">
         <v>275</v>
@@ -1984,20 +1984,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="D37" t="n">
         <v>18</v>
       </c>
       <c r="E37" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="F37" t="n">
-        <v>122.4</v>
+        <v>172.4</v>
       </c>
       <c r="G37" t="n">
         <v>20</v>
@@ -2006,13 +2006,13 @@
         <v>10</v>
       </c>
       <c r="I37" t="n">
-        <v>164.8</v>
+        <v>215</v>
       </c>
       <c r="J37" t="n">
-        <v>160.3</v>
+        <v>210.5</v>
       </c>
       <c r="K37" t="n">
-        <v>169.3</v>
+        <v>219.5</v>
       </c>
       <c r="L37" t="n">
         <v>275</v>
@@ -2021,343 +2021,343 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="C38" t="n">
+        <v>177</v>
+      </c>
+      <c r="D38" t="n">
+        <v>18</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F38" t="n">
         <v>160</v>
       </c>
-      <c r="D38" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>212.9</v>
-      </c>
       <c r="G38" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I38" t="n">
-        <v>272.4</v>
+        <v>202.5</v>
       </c>
       <c r="J38" t="n">
-        <v>264.1</v>
+        <v>198</v>
       </c>
       <c r="K38" t="n">
-        <v>280.7</v>
+        <v>207</v>
       </c>
       <c r="L38" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>200</v>
       </c>
       <c r="D39" t="n">
-        <v>41.5</v>
+        <v>18</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="F39" t="n">
-        <v>191.8</v>
+        <v>148</v>
       </c>
       <c r="G39" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I39" t="n">
-        <v>251.3</v>
+        <v>190.4</v>
       </c>
       <c r="J39" t="n">
-        <v>243</v>
+        <v>185.9</v>
       </c>
       <c r="K39" t="n">
-        <v>259.6</v>
+        <v>194.9</v>
       </c>
       <c r="L39" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>250</v>
       </c>
       <c r="D40" t="n">
-        <v>41.5</v>
+        <v>18</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="F40" t="n">
-        <v>184.7</v>
+        <v>134</v>
       </c>
       <c r="G40" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I40" t="n">
-        <v>244.2</v>
+        <v>176.5</v>
       </c>
       <c r="J40" t="n">
-        <v>235.9</v>
+        <v>172</v>
       </c>
       <c r="K40" t="n">
-        <v>252.5</v>
+        <v>180.9</v>
       </c>
       <c r="L40" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>300</v>
       </c>
       <c r="D41" t="n">
-        <v>41.5</v>
+        <v>18</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="F41" t="n">
-        <v>183.9</v>
+        <v>129.6</v>
       </c>
       <c r="G41" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I41" t="n">
-        <v>243.4</v>
+        <v>172</v>
       </c>
       <c r="J41" t="n">
-        <v>235.1</v>
+        <v>167.6</v>
       </c>
       <c r="K41" t="n">
-        <v>251.7</v>
+        <v>176.5</v>
       </c>
       <c r="L41" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>160</v>
       </c>
       <c r="D42" t="n">
-        <v>41.5</v>
+        <v>18</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="F42" t="n">
-        <v>204.8</v>
+        <v>171.7</v>
       </c>
       <c r="G42" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I42" t="n">
-        <v>264.3</v>
+        <v>214.3</v>
       </c>
       <c r="J42" t="n">
-        <v>256</v>
+        <v>209.7</v>
       </c>
       <c r="K42" t="n">
-        <v>272.6</v>
+        <v>218.8</v>
       </c>
       <c r="L42" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D43" t="n">
-        <v>41.5</v>
+        <v>18</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="F43" t="n">
-        <v>174.6</v>
+        <v>158.8</v>
       </c>
       <c r="G43" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I43" t="n">
-        <v>234.1</v>
+        <v>201.3</v>
       </c>
       <c r="J43" t="n">
-        <v>225.8</v>
+        <v>196.8</v>
       </c>
       <c r="K43" t="n">
-        <v>242.4</v>
+        <v>205.8</v>
       </c>
       <c r="L43" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="D44" t="n">
-        <v>41.5</v>
+        <v>18</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="F44" t="n">
-        <v>155.6</v>
+        <v>145.7</v>
       </c>
       <c r="G44" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I44" t="n">
-        <v>215.1</v>
+        <v>188.2</v>
       </c>
       <c r="J44" t="n">
-        <v>206.8</v>
+        <v>183.7</v>
       </c>
       <c r="K44" t="n">
-        <v>223.4</v>
+        <v>192.7</v>
       </c>
       <c r="L44" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="D45" t="n">
-        <v>41.5</v>
+        <v>18</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="F45" t="n">
-        <v>148.5</v>
+        <v>127.1</v>
       </c>
       <c r="G45" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I45" t="n">
-        <v>208</v>
+        <v>169.5</v>
       </c>
       <c r="J45" t="n">
-        <v>199.7</v>
+        <v>165</v>
       </c>
       <c r="K45" t="n">
-        <v>216.3</v>
+        <v>174</v>
       </c>
       <c r="L45" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2366,34 +2366,34 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>160</v>
+        <v>300</v>
       </c>
       <c r="D46" t="n">
-        <v>41.5</v>
+        <v>18</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="F46" t="n">
-        <v>203.4</v>
+        <v>119.9</v>
       </c>
       <c r="G46" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I46" t="n">
-        <v>262.9</v>
+        <v>162.3</v>
       </c>
       <c r="J46" t="n">
-        <v>254.6</v>
+        <v>157.8</v>
       </c>
       <c r="K46" t="n">
-        <v>271.2</v>
+        <v>166.8</v>
       </c>
       <c r="L46" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="47">
@@ -2404,11 +2404,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="D47" t="n">
         <v>41.5</v>
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>171.7</v>
+        <v>209.7</v>
       </c>
       <c r="G47" t="n">
         <v>18</v>
@@ -2426,13 +2426,13 @@
         <v>9</v>
       </c>
       <c r="I47" t="n">
-        <v>231.2</v>
+        <v>269.2</v>
       </c>
       <c r="J47" t="n">
-        <v>222.9</v>
+        <v>260.9</v>
       </c>
       <c r="K47" t="n">
-        <v>239.5</v>
+        <v>277.5</v>
       </c>
       <c r="L47" t="n">
         <v>318</v>
@@ -2446,11 +2446,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>250</v>
+        <v>177</v>
       </c>
       <c r="D48" t="n">
         <v>41.5</v>
@@ -2459,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>148.2</v>
+        <v>197.6</v>
       </c>
       <c r="G48" t="n">
         <v>18</v>
@@ -2468,13 +2468,13 @@
         <v>9</v>
       </c>
       <c r="I48" t="n">
-        <v>207.7</v>
+        <v>257.1</v>
       </c>
       <c r="J48" t="n">
-        <v>199.4</v>
+        <v>248.8</v>
       </c>
       <c r="K48" t="n">
-        <v>216</v>
+        <v>265.4</v>
       </c>
       <c r="L48" t="n">
         <v>318</v>
@@ -2488,11 +2488,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D49" t="n">
         <v>41.5</v>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>138</v>
+        <v>187.3</v>
       </c>
       <c r="G49" t="n">
         <v>18</v>
@@ -2510,20 +2510,524 @@
         <v>9</v>
       </c>
       <c r="I49" t="n">
-        <v>197.5</v>
+        <v>246.8</v>
       </c>
       <c r="J49" t="n">
-        <v>189.2</v>
+        <v>238.5</v>
       </c>
       <c r="K49" t="n">
-        <v>205.8</v>
+        <v>255.1</v>
       </c>
       <c r="L49" t="n">
         <v>318</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>250</v>
+      </c>
+      <c r="D50" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="G50" t="n">
+        <v>18</v>
+      </c>
+      <c r="H50" t="n">
+        <v>9</v>
+      </c>
+      <c r="I50" t="n">
+        <v>239.1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>230.8</v>
+      </c>
+      <c r="K50" t="n">
+        <v>247.4</v>
+      </c>
+      <c r="L50" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>300</v>
+      </c>
+      <c r="D51" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="G51" t="n">
+        <v>18</v>
+      </c>
+      <c r="H51" t="n">
+        <v>9</v>
+      </c>
+      <c r="I51" t="n">
+        <v>239.1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>230.8</v>
+      </c>
+      <c r="K51" t="n">
+        <v>247.4</v>
+      </c>
+      <c r="L51" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>160</v>
+      </c>
+      <c r="D52" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="G52" t="n">
+        <v>18</v>
+      </c>
+      <c r="H52" t="n">
+        <v>9</v>
+      </c>
+      <c r="I52" t="n">
+        <v>263</v>
+      </c>
+      <c r="J52" t="n">
+        <v>254.7</v>
+      </c>
+      <c r="K52" t="n">
+        <v>271.3</v>
+      </c>
+      <c r="L52" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>177</v>
+      </c>
+      <c r="D53" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>187.8</v>
+      </c>
+      <c r="G53" t="n">
+        <v>18</v>
+      </c>
+      <c r="H53" t="n">
+        <v>9</v>
+      </c>
+      <c r="I53" t="n">
+        <v>247.3</v>
+      </c>
+      <c r="J53" t="n">
+        <v>239</v>
+      </c>
+      <c r="K53" t="n">
+        <v>255.6</v>
+      </c>
+      <c r="L53" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>200</v>
+      </c>
+      <c r="D54" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>171.9</v>
+      </c>
+      <c r="G54" t="n">
+        <v>18</v>
+      </c>
+      <c r="H54" t="n">
+        <v>9</v>
+      </c>
+      <c r="I54" t="n">
+        <v>231.4</v>
+      </c>
+      <c r="J54" t="n">
+        <v>223.1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>239.7</v>
+      </c>
+      <c r="L54" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>250</v>
+      </c>
+      <c r="D55" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>152.2</v>
+      </c>
+      <c r="G55" t="n">
+        <v>18</v>
+      </c>
+      <c r="H55" t="n">
+        <v>9</v>
+      </c>
+      <c r="I55" t="n">
+        <v>211.7</v>
+      </c>
+      <c r="J55" t="n">
+        <v>203.4</v>
+      </c>
+      <c r="K55" t="n">
+        <v>220</v>
+      </c>
+      <c r="L55" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>300</v>
+      </c>
+      <c r="D56" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>144.8</v>
+      </c>
+      <c r="G56" t="n">
+        <v>18</v>
+      </c>
+      <c r="H56" t="n">
+        <v>9</v>
+      </c>
+      <c r="I56" t="n">
+        <v>204.3</v>
+      </c>
+      <c r="J56" t="n">
+        <v>196</v>
+      </c>
+      <c r="K56" t="n">
+        <v>212.6</v>
+      </c>
+      <c r="L56" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>160</v>
+      </c>
+      <c r="D57" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>203</v>
+      </c>
+      <c r="G57" t="n">
+        <v>18</v>
+      </c>
+      <c r="H57" t="n">
+        <v>9</v>
+      </c>
+      <c r="I57" t="n">
+        <v>262.5</v>
+      </c>
+      <c r="J57" t="n">
+        <v>254.2</v>
+      </c>
+      <c r="K57" t="n">
+        <v>270.8</v>
+      </c>
+      <c r="L57" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>177</v>
+      </c>
+      <c r="D58" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>186.9</v>
+      </c>
+      <c r="G58" t="n">
+        <v>18</v>
+      </c>
+      <c r="H58" t="n">
+        <v>9</v>
+      </c>
+      <c r="I58" t="n">
+        <v>246.4</v>
+      </c>
+      <c r="J58" t="n">
+        <v>238.1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>254.7</v>
+      </c>
+      <c r="L58" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>200</v>
+      </c>
+      <c r="D59" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>170.3</v>
+      </c>
+      <c r="G59" t="n">
+        <v>18</v>
+      </c>
+      <c r="H59" t="n">
+        <v>9</v>
+      </c>
+      <c r="I59" t="n">
+        <v>229.8</v>
+      </c>
+      <c r="J59" t="n">
+        <v>221.5</v>
+      </c>
+      <c r="K59" t="n">
+        <v>238.1</v>
+      </c>
+      <c r="L59" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>250</v>
+      </c>
+      <c r="D60" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>145.7</v>
+      </c>
+      <c r="G60" t="n">
+        <v>18</v>
+      </c>
+      <c r="H60" t="n">
+        <v>9</v>
+      </c>
+      <c r="I60" t="n">
+        <v>205.2</v>
+      </c>
+      <c r="J60" t="n">
+        <v>196.9</v>
+      </c>
+      <c r="K60" t="n">
+        <v>213.5</v>
+      </c>
+      <c r="L60" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>300</v>
+      </c>
+      <c r="D61" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="G61" t="n">
+        <v>18</v>
+      </c>
+      <c r="H61" t="n">
+        <v>9</v>
+      </c>
+      <c r="I61" t="n">
+        <v>194.3</v>
+      </c>
+      <c r="J61" t="n">
+        <v>186</v>
+      </c>
+      <c r="K61" t="n">
+        <v>202.6</v>
+      </c>
+      <c r="L61" t="n">
+        <v>318</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L49"/>
+  <autoFilter ref="A1:L61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/livrables/tbase_par_bande.xlsx
+++ b/livrables/tbase_par_bande.xlsx
@@ -431,7 +431,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -514,7 +514,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -598,7 +598,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -640,7 +640,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -682,7 +682,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -724,7 +724,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -808,7 +808,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -850,7 +850,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -892,7 +892,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -934,7 +934,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C61" t="n">
